--- a/material_order_forms/012_fitness_studio_window_branding_order_form--material_order_forms.xlsx
+++ b/material_order_forms/012_fitness_studio_window_branding_order_form--material_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1286,8 +1286,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1519,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1553,12 +1553,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1587,12 +1587,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1621,12 +1621,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1655,12 +1655,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1740,12 +1740,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1825,12 +1825,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1842,12 +1842,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1876,12 +1876,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1910,12 +1910,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1961,12 +1961,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1995,12 +1995,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2012,12 +2012,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2029,12 +2029,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2063,12 +2063,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2080,12 +2080,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2131,12 +2131,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2148,12 +2148,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2182,12 +2182,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2199,12 +2199,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2250,12 +2250,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2267,12 +2267,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2301,12 +2301,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2369,12 +2369,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2386,12 +2386,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2420,12 +2420,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2454,12 +2454,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2471,12 +2471,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2488,12 +2488,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2505,12 +2505,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2539,12 +2539,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2590,12 +2590,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2607,12 +2607,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2624,12 +2624,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
